--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/tyche.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/tyche.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="tyche" sheetId="1" r:id="rId3"/>
+    <sheet name="tyche" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="72">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -270,86 +270,6 @@
   </si>
   <si>
     <t xml:space="preserve">...GOOD BYE.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">狩猎人造人真是太好玩了！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你有什么工作吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">任务完成了</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嘿，你！
-我有份很厉害的工作给你，说不定你会成为人类的救世主哦☆</t>
-  </si>
-  <si>
-    <t xml:space="preserve">接受委托（危险度相当于38层）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">还是算了吧</t>
-  </si>
-  <si>
-    <t xml:space="preserve">聪明的选择呢♡　绝对不会让你后悔的！
-啊，我还没自我介绍呢。请叫我缇克☆
-然后这边是我的伙伴VISHNU。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…今后请您多多关照。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那我就进入正题了。你以前吃过咖喱吗？☆
-那是种超级美味，只要吃过一回就会让人上瘾的料理。我们旅行就是为了找到各种咖喱。
-跟你说，这个「龙与香辛料」的咖喱味道简直让人上天了！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">肉、蔬菜、香辛料，这里的咖喱无论在哪方面都是我们至今为止从未遇到过的极致水平。这可不同寻常…你懂我意思吧？
-如果能够弄清楚构成这味道的秘密，人类的文化就可以进步到下一阶段…这么说虽然有点夸张…但你一定懂这种感觉吧？　
-…所以这当然得调查一下吧？♡</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不过退一步讲，店开在这么偏僻的地方也挺奇怪啊。
-那个遗迹也是，你没闻到什么吗？　地下说不定藏着什么不得了的食材！
-这对于一个柔弱的少女还有一台破烂机器人而言实在是太难了…就是这样，你愿意帮忙吧？　你会帮忙吧？　嗯？♡</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哈～，你是个通情达理的冒险者真是太好了♡
-我们就在这里等着，探索地下遗迹的事就拜托你啦☆</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…路上小心。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哦？　啊～？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你安全回来了啊☆
-刚才感觉地面晃的好厉害…什么？地下有机器人们运营的工厂？你还被巨大机器人袭击了！？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">原来如此。
-那肯定是艾斯·泰尔时代的地下农场。就算人类已经不在了，那里的机器也没有停止继续生产食物。
-所以咖喱店的店主是用了遗迹里发现的食材，才制作出了那么美味的咖喱吗…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…怎会如此。真是悲剧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没…没事的！　那个店主那么厉害，就算没了地下农场也一定能想到其他办法☆
-不过#pc也要记住哦，虽然你身为冒险者，但冒险的结局也并非总是好的哦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">给，这是我珍藏的种子，送给你，打起精神来哦♡
-我觉得不如这么想，我们给予了失去本来任务还不断工作的可悲机器们安息！
-那么，我们要趁着还没暴露的时候跑路了☆
-…对了，如果种子不够的话，可以和这里的店主买哦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…再见，再见。</t>
   </si>
 </sst>
 </file>
@@ -370,25 +290,25 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -408,7 +328,7 @@
     <font>
       <sz val="10"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -421,7 +341,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -440,7 +360,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -449,98 +369,98 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="17">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -554,13 +474,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -736,26 +656,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L49"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.85" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
-    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
-    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
-    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
-    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.06"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -793,24 +713,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="I2" s="1">
-        <f>MAX(I4:I1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="1" t="n">
+        <f aca="false">MAX(I4:I1048576)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="13.8">
-      <c r="I8" s="1">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -819,11 +739,8 @@
       <c r="K8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="L8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" ht="13.8">
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
@@ -836,7 +753,7 @@
       <c r="E9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J9" s="5" t="s">
@@ -845,11 +762,8 @@
       <c r="K9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" ht="13.8">
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
         <v>22</v>
       </c>
@@ -862,7 +776,7 @@
       <c r="E10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J10" s="5" t="s">
@@ -871,11 +785,8 @@
       <c r="K10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" ht="12.8">
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E11" s="1" t="s">
         <v>26</v>
       </c>
@@ -883,23 +794,23 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" ht="12.8">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E12" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" ht="12.8">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E13" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" ht="12.8">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" ht="43.25">
-      <c r="I16" s="1">
+    <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I16" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J16" s="3" t="s">
@@ -908,18 +819,15 @@
       <c r="K16" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="L16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" ht="12.8">
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J17" s="7" t="s">
@@ -928,18 +836,15 @@
       <c r="K17" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="L17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" ht="12.8">
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I18" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J18" s="7" t="s">
@@ -948,11 +853,8 @@
       <c r="K18" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="L18" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" ht="12.8">
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
         <v>35</v>
       </c>
@@ -960,12 +862,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" ht="12.8">
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23" ht="12.8">
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E23" s="1" t="s">
         <v>38</v>
       </c>
@@ -973,13 +875,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" ht="12.8">
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E24" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="26" ht="49.95">
-      <c r="I26" s="1">
+    <row r="26" customFormat="false" ht="49.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I26" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J26" s="9" t="s">
@@ -988,15 +890,12 @@
       <c r="K26" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L26" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" ht="12.8">
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G27" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I27" s="1">
+      <c r="I27" s="1" t="n">
         <v>8</v>
       </c>
       <c r="J27" s="10" t="s">
@@ -1005,16 +904,13 @@
       <c r="K27" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="L27" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" ht="13.8">
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
     </row>
-    <row r="29" ht="79.1">
-      <c r="I29" s="1">
+    <row r="29" customFormat="false" ht="79.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I29" s="1" t="n">
         <v>9</v>
       </c>
       <c r="J29" s="10" t="s">
@@ -1023,12 +919,9 @@
       <c r="K29" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="L29" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="30" ht="94">
-      <c r="I30" s="1">
+    </row>
+    <row r="30" customFormat="false" ht="94" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I30" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J30" s="10" t="s">
@@ -1037,12 +930,9 @@
       <c r="K30" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="L30" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31" ht="105.95">
-      <c r="I31" s="1">
+    </row>
+    <row r="31" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I31" s="1" t="n">
         <v>11</v>
       </c>
       <c r="J31" s="10" t="s">
@@ -1051,12 +941,9 @@
       <c r="K31" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="L31" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" ht="36.55">
-      <c r="I32" s="1">
+    </row>
+    <row r="32" customFormat="false" ht="36.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I32" s="1" t="n">
         <v>12</v>
       </c>
       <c r="J32" s="10" t="s">
@@ -1065,15 +952,12 @@
       <c r="K32" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="L32" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" ht="12.8">
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G33" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I33" s="1">
+      <c r="I33" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J33" s="10" t="s">
@@ -1082,22 +966,19 @@
       <c r="K33" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="L33" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="34" ht="12.8">
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="36" ht="12.8">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" ht="23.85">
-      <c r="I37" s="1">
+    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I37" s="1" t="n">
         <v>13</v>
       </c>
       <c r="J37" s="5" t="s">
@@ -1106,22 +987,19 @@
       <c r="K37" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="L37" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="38" ht="12.8">
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="41" ht="12.8">
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="42" ht="47.75">
-      <c r="I42" s="1">
+    <row r="42" customFormat="false" ht="47.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I42" s="1" t="n">
         <v>14</v>
       </c>
       <c r="J42" s="14" t="s">
@@ -1130,12 +1008,9 @@
       <c r="K42" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="L42" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" ht="94">
-      <c r="I43" s="1">
+    </row>
+    <row r="43" customFormat="false" ht="94" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I43" s="1" t="n">
         <v>15</v>
       </c>
       <c r="J43" s="15" t="s">
@@ -1144,15 +1019,12 @@
       <c r="K43" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="L43" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="44" ht="13.8">
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G44" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I44" s="1">
+      <c r="I44" s="1" t="n">
         <v>16</v>
       </c>
       <c r="J44" s="16" t="s">
@@ -1161,12 +1033,9 @@
       <c r="K44" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="L44" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="45" ht="58.95">
-      <c r="I45" s="1">
+    </row>
+    <row r="45" customFormat="false" ht="58.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I45" s="1" t="n">
         <v>17</v>
       </c>
       <c r="J45" s="15" t="s">
@@ -1175,11 +1044,8 @@
       <c r="K45" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="L45" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="46" ht="12.8">
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E46" s="1" t="s">
         <v>67</v>
       </c>
@@ -1187,8 +1053,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="47" ht="106.7">
-      <c r="I47" s="1">
+    <row r="47" customFormat="false" ht="106.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I47" s="1" t="n">
         <v>18</v>
       </c>
       <c r="J47" s="15" t="s">
@@ -1197,15 +1063,12 @@
       <c r="K47" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="L47" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="48" ht="13.8">
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G48" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I48" s="1">
+      <c r="I48" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J48" s="16" t="s">
@@ -1214,23 +1077,20 @@
       <c r="K48" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="L48" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="49" ht="12.8">
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="1" t="s">
         <v>56</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/tyche.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/tyche.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="tyche" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="tyche" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="93">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -270,6 +270,86 @@
   </si>
   <si>
     <t xml:space="preserve">...GOOD BYE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">狩猎人造人真是太好玩了！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你有什么工作吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">任务完成了</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嘿，你！
+我有份很厉害的工作给你，说不定你会成为人类的救世主哦☆</t>
+  </si>
+  <si>
+    <t xml:space="preserve">接受委托（危险度相当于38层）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">还是算了吧</t>
+  </si>
+  <si>
+    <t xml:space="preserve">聪明的选择呢♡　绝对不会让你后悔的！
+啊，我还没自我介绍呢。请叫我缇克☆
+然后这边是我的伙伴VISHNU。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…今后请您多多关照。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那我就进入正题了。你以前吃过咖喱吗？☆
+那是种超级美味，只要吃过一回就会让人上瘾的料理。我们旅行就是为了找到各种咖喱。
+跟你说，这个「龙与香辛料」的咖喱味道简直让人上天了！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">肉、蔬菜、香辛料，这里的咖喱无论在哪方面都是我们至今为止从未遇到过的极致水平。这可不同寻常…你懂我意思吧？
+如果能够弄清楚构成这味道的秘密，人类的文化就可以进步到下一阶段…这么说虽然有点夸张…但你一定懂这种感觉吧？　
+…所以这当然得调查一下吧？♡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不过退一步讲，店开在这么偏僻的地方也挺奇怪啊。
+那个遗迹也是，你没闻到什么吗？　地下说不定藏着什么不得了的食材！
+这对于一个柔弱的少女还有一台破烂机器人而言实在是太难了…就是这样，你愿意帮忙吧？　你会帮忙吧？　嗯？♡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哈～，你是个通情达理的冒险者真是太好了♡
+我们就在这里等着，探索地下遗迹的事就拜托你啦☆</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…路上小心。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哦？　啊～？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你安全回来了啊☆
+刚才感觉地面晃的好厉害…什么？地下有机器人们运营的工厂？你还被巨大机器人袭击了！？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">原来如此。
+那肯定是艾斯·泰尔时代的地下农场。就算人类已经不在了，那里的机器也没有停止继续生产食物。
+所以咖喱店的店主是用了遗迹里发现的食材，才制作出了那么美味的咖喱吗…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…怎会如此。真是悲剧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没…没事的！　那个店主那么厉害，就算没了地下农场也一定能想到其他办法☆
+不过#pc也要记住哦，虽然你身为冒险者，但冒险的结局也并非总是好的哦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">给，这是我珍藏的种子，送给你，打起精神来哦♡
+我觉得不如这么想，我们给予了失去本来任务还不断工作的可悲机器们安息！
+那么，我们要趁着还没暴露的时候跑路了☆
+…对了，如果种子不够的话，可以和这里的店主买哦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…再见，再见。</t>
   </si>
 </sst>
 </file>
@@ -290,25 +370,25 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -328,7 +408,7 @@
     <font>
       <sz val="10"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -341,7 +421,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -360,7 +440,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -369,98 +449,98 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -474,13 +554,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -656,26 +736,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L49"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.06"/>
+    <col min="1" max="1" width="8.85" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
+    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
+    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
+    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
+    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -713,24 +793,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I2" s="1" t="n">
-        <f aca="false">MAX(I4:I1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="I2" s="1">
+        <f>MAX(I4:I1048576)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I8" s="1" t="n">
+    <row r="8" ht="13.8">
+      <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -739,8 +819,11 @@
       <c r="K8" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" ht="13.8">
       <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
@@ -753,7 +836,7 @@
       <c r="E9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="1" t="n">
+      <c r="I9" s="1">
         <v>2</v>
       </c>
       <c r="J9" s="5" t="s">
@@ -762,8 +845,11 @@
       <c r="K9" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" ht="13.8">
       <c r="B10" s="1" t="s">
         <v>22</v>
       </c>
@@ -776,7 +862,7 @@
       <c r="E10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I10" s="1" t="n">
+      <c r="I10" s="1">
         <v>3</v>
       </c>
       <c r="J10" s="5" t="s">
@@ -785,8 +871,11 @@
       <c r="K10" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" ht="12.8">
       <c r="E11" s="1" t="s">
         <v>26</v>
       </c>
@@ -794,23 +883,23 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.8">
       <c r="E12" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="12.8">
       <c r="E13" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="12.8">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I16" s="1" t="n">
+    <row r="16" ht="43.25">
+      <c r="I16" s="1">
         <v>4</v>
       </c>
       <c r="J16" s="3" t="s">
@@ -819,15 +908,18 @@
       <c r="K16" s="6" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" ht="12.8">
       <c r="B17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I17" s="1" t="n">
+      <c r="I17" s="1">
         <v>5</v>
       </c>
       <c r="J17" s="7" t="s">
@@ -836,15 +928,18 @@
       <c r="K17" s="7" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" ht="12.8">
       <c r="B18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I18" s="1" t="n">
+      <c r="I18" s="1">
         <v>6</v>
       </c>
       <c r="J18" s="7" t="s">
@@ -853,8 +948,11 @@
       <c r="K18" s="7" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L18" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" ht="12.8">
       <c r="B19" s="1" t="s">
         <v>35</v>
       </c>
@@ -862,12 +960,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" ht="12.8">
       <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" ht="12.8">
       <c r="E23" s="1" t="s">
         <v>38</v>
       </c>
@@ -875,13 +973,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" ht="12.8">
       <c r="E24" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="49.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I26" s="1" t="n">
+    <row r="26" ht="49.95">
+      <c r="I26" s="1">
         <v>7</v>
       </c>
       <c r="J26" s="9" t="s">
@@ -890,12 +988,15 @@
       <c r="K26" s="9" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" ht="12.8">
       <c r="G27" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I27" s="1" t="n">
+      <c r="I27" s="1">
         <v>8</v>
       </c>
       <c r="J27" s="10" t="s">
@@ -904,13 +1005,16 @@
       <c r="K27" s="11" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L27" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" ht="13.8">
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
     </row>
-    <row r="29" customFormat="false" ht="79.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I29" s="1" t="n">
+    <row r="29" ht="79.1">
+      <c r="I29" s="1">
         <v>9</v>
       </c>
       <c r="J29" s="10" t="s">
@@ -919,9 +1023,12 @@
       <c r="K29" s="9" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="94" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I30" s="1" t="n">
+      <c r="L29" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" ht="94">
+      <c r="I30" s="1">
         <v>10</v>
       </c>
       <c r="J30" s="10" t="s">
@@ -930,9 +1037,12 @@
       <c r="K30" s="12" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I31" s="1" t="n">
+      <c r="L30" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" ht="105.95">
+      <c r="I31" s="1">
         <v>11</v>
       </c>
       <c r="J31" s="10" t="s">
@@ -941,9 +1051,12 @@
       <c r="K31" s="7" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="36.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I32" s="1" t="n">
+      <c r="L31" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" ht="36.55">
+      <c r="I32" s="1">
         <v>12</v>
       </c>
       <c r="J32" s="10" t="s">
@@ -952,12 +1065,15 @@
       <c r="K32" s="13" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L32" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" ht="12.8">
       <c r="G33" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I33" s="1" t="n">
+      <c r="I33" s="1">
         <v>20</v>
       </c>
       <c r="J33" s="10" t="s">
@@ -966,19 +1082,22 @@
       <c r="K33" s="13" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L33" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" ht="12.8">
       <c r="B34" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" ht="12.8">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I37" s="1" t="n">
+    <row r="37" ht="23.85">
+      <c r="I37" s="1">
         <v>13</v>
       </c>
       <c r="J37" s="5" t="s">
@@ -987,19 +1106,22 @@
       <c r="K37" s="13" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L37" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" ht="12.8">
       <c r="B38" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" ht="12.8">
       <c r="A41" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="47.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I42" s="1" t="n">
+    <row r="42" ht="47.75">
+      <c r="I42" s="1">
         <v>14</v>
       </c>
       <c r="J42" s="14" t="s">
@@ -1008,9 +1130,12 @@
       <c r="K42" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="94" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I43" s="1" t="n">
+      <c r="L42" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" ht="94">
+      <c r="I43" s="1">
         <v>15</v>
       </c>
       <c r="J43" s="15" t="s">
@@ -1019,12 +1144,15 @@
       <c r="K43" s="4" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" ht="13.8">
       <c r="G44" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I44" s="1" t="n">
+      <c r="I44" s="1">
         <v>16</v>
       </c>
       <c r="J44" s="16" t="s">
@@ -1033,9 +1161,12 @@
       <c r="K44" s="4" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="58.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I45" s="1" t="n">
+      <c r="L44" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="45" ht="58.95">
+      <c r="I45" s="1">
         <v>17</v>
       </c>
       <c r="J45" s="15" t="s">
@@ -1044,8 +1175,11 @@
       <c r="K45" s="4" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L45" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" ht="12.8">
       <c r="E46" s="1" t="s">
         <v>67</v>
       </c>
@@ -1053,8 +1187,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="106.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I47" s="1" t="n">
+    <row r="47" ht="106.7">
+      <c r="I47" s="1">
         <v>18</v>
       </c>
       <c r="J47" s="15" t="s">
@@ -1063,12 +1197,15 @@
       <c r="K47" s="4" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L47" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" ht="13.8">
       <c r="G48" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I48" s="1" t="n">
+      <c r="I48" s="1">
         <v>19</v>
       </c>
       <c r="J48" s="16" t="s">
@@ -1077,20 +1214,23 @@
       <c r="K48" s="4" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L48" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" ht="12.8">
       <c r="B49" s="1" t="s">
         <v>56</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
